--- a/output/pdf_financials_xlsx/E.xlsx
+++ b/output/pdf_financials_xlsx/E.xlsx
@@ -7857,10 +7857,10 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>-4.311494</v>
+        <v>-7.474864</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>-2.51503</v>
+        <v>-5.87856</v>
       </c>
       <c r="D124" s="3" t="n">
         <v>0</v>
@@ -7917,10 +7917,10 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>-3.134355</v>
+        <v>-6.297725</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>-1.236029</v>
+        <v>-4.599559</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>0</v>
@@ -36240,7 +36240,11 @@
           <t>Repayment of bank indebtedness</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr"/>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E285" s="5" t="n">
         <v>-3.16337</v>
       </c>

--- a/output/pdf_financials_xlsx/E.xlsx
+++ b/output/pdf_financials_xlsx/E.xlsx
@@ -2122,16 +2122,16 @@
         <v>0.1455</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0.1455</v>
+        <v>1.570339</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0.1455</v>
+        <v>1.259252</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0.165012</v>
+        <v>1.464411</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.314172</v>
+        <v>2.671257</v>
       </c>
       <c r="G28" s="1" t="inlineStr">
         <is>
@@ -2139,16 +2139,16 @@
         </is>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0.729341</v>
+        <v>7.480492</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.367442</v>
+        <v>6.915296</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.30422</v>
+        <v>5.970957</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0.373391</v>
+        <v>5.796549</v>
       </c>
       <c r="L28" s="1" t="inlineStr">
         <is>
@@ -2156,22 +2156,22 @@
         </is>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0.094371</v>
+        <v>6.118298</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0.060519</v>
+        <v>5.856215</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0.054691</v>
+        <v>4.520771</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0.050322</v>
+        <v>5.005936</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>0.050143</v>
+        <v>5.248883</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>0.060481</v>
+        <v>5.483827</v>
       </c>
     </row>
     <row r="29">
@@ -2184,16 +2184,16 @@
         <v>-5.667798</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-3.318918</v>
+        <v>-1.894079</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.224374</v>
+        <v>1.338126</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>2.303934</v>
+        <v>3.603333</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>5.335157</v>
+        <v>7.692242</v>
       </c>
       <c r="G29" s="1" t="inlineStr">
         <is>
@@ -2201,16 +2201,16 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-22.521154</v>
+        <v>-15.770003</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-15.185709</v>
+        <v>-8.637855</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.74455</v>
+        <v>4.922187</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-5.439112</v>
+        <v>-0.015954</v>
       </c>
       <c r="L29" s="1" t="inlineStr">
         <is>
@@ -2218,22 +2218,22 @@
         </is>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-4.632811</v>
+        <v>1.391116</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-2.35789</v>
+        <v>3.437806</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>2.328986</v>
+        <v>6.795066</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>6.220226</v>
+        <v>11.17584</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>4.718944</v>
+        <v>9.917684</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>4.604959</v>
+        <v>10.028305</v>
       </c>
     </row>
     <row r="30">
@@ -2246,16 +2246,16 @@
         <v>-20.46177681124407</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-21.2431308552866</v>
+        <v>-12.12327874543764</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>1.254627674612519</v>
+        <v>7.482372787036606</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>12.45098634740501</v>
+        <v>19.47323577331379</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>15.30923778997239</v>
+        <v>22.07289530861281</v>
       </c>
       <c r="G30" s="1" t="inlineStr">
         <is>
@@ -2263,16 +2263,16 @@
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-56.65023734654628</v>
+        <v>-39.66823427013318</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-52.86843198716317</v>
+        <v>-30.07234298921949</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-1.97613310020156</v>
+        <v>13.06412820640899</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-22.34680775501665</v>
+        <v>-0.06554764287323658</v>
       </c>
       <c r="L30" s="1" t="inlineStr">
         <is>
@@ -2280,22 +2280,22 @@
         </is>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-29.85038438850768</v>
+        <v>8.963315647671198</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-12.58727222206949</v>
+        <v>18.35225560508073</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>8.660435949406835</v>
+        <v>25.26774908264459</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>18.56756112393662</v>
+        <v>33.36021750838891</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>13.62010925772035</v>
+        <v>28.62503552988655</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>12.6671236224346</v>
+        <v>27.5854310881984</v>
       </c>
     </row>
     <row r="31">
@@ -6415,34 +6415,34 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.1455</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>1.570339</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>1.259252</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>1.464411</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>2.671257</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>7.14846</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>9.313858</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>8.010476000000001</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>5.970957</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>5.796549</v>
       </c>
       <c r="L100" s="1" t="inlineStr">
         <is>
@@ -6450,22 +6450,22 @@
         </is>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>6.118298</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>5.856215</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>4.520771</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>5.005936</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>5.248883</v>
       </c>
       <c r="R100" s="3" t="n">
-        <v>0</v>
+        <v>5.483827</v>
       </c>
     </row>
     <row r="101">
@@ -22976,7 +22976,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
           <t>-</t>
@@ -23049,7 +23053,11 @@
           <t>Depreciation of right-of-use assets</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
           <t>-</t>
@@ -23142,7 +23150,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -35535,7 +35543,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E278" s="5" t="n">
@@ -38275,7 +38283,11 @@
           <t>Depreciation of property, plant and equipment (note 6)</t>
         </is>
       </c>
-      <c r="D306" t="inlineStr"/>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E306" t="inlineStr">
         <is>
           <t>-</t>
@@ -38352,10 +38364,10 @@
         </is>
       </c>
       <c r="T306" s="5" t="n">
-        <v>-3.69693</v>
+        <v>3.69693</v>
       </c>
       <c r="U306" s="5" t="n">
-        <v>-3.871497</v>
+        <v>3.871497</v>
       </c>
     </row>
     <row r="307">
@@ -38370,7 +38382,11 @@
           <t>Depreciation of right-of-use assets (note 6)</t>
         </is>
       </c>
-      <c r="D307" t="inlineStr"/>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E307" t="inlineStr">
         <is>
           <t>-</t>
@@ -38447,10 +38463,10 @@
         </is>
       </c>
       <c r="T307" s="5" t="n">
-        <v>-1.50181</v>
+        <v>1.50181</v>
       </c>
       <c r="U307" s="5" t="n">
-        <v>-1.551849</v>
+        <v>1.551849</v>
       </c>
     </row>
     <row r="308">
@@ -38550,7 +38566,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -38629,10 +38645,10 @@
         </is>
       </c>
       <c r="T309" s="5" t="n">
-        <v>-0.050143</v>
+        <v>0.050143</v>
       </c>
       <c r="U309" s="5" t="n">
-        <v>-0.060481</v>
+        <v>0.060481</v>
       </c>
     </row>
     <row r="310">
@@ -39888,7 +39904,11 @@
           <t>Depreciation of property, plant and equipment (note 5)</t>
         </is>
       </c>
-      <c r="D323" t="inlineStr"/>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E323" t="inlineStr">
         <is>
           <t>-</t>
@@ -39945,19 +39965,19 @@
         </is>
       </c>
       <c r="P323" s="5" t="n">
-        <v>-5.491729</v>
+        <v>5.491729</v>
       </c>
       <c r="Q323" s="5" t="n">
-        <v>-5.119474</v>
+        <v>5.119474</v>
       </c>
       <c r="R323" s="5" t="n">
-        <v>-3.914208</v>
+        <v>3.914208</v>
       </c>
       <c r="S323" s="5" t="n">
-        <v>-4.463819</v>
+        <v>4.463819</v>
       </c>
       <c r="T323" s="5" t="n">
-        <v>-3.69693</v>
+        <v>3.69693</v>
       </c>
       <c r="U323" t="inlineStr">
         <is>
@@ -39977,7 +39997,11 @@
           <t>Depreciation of right-of-use assets (note 5)</t>
         </is>
       </c>
-      <c r="D324" t="inlineStr"/>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E324" t="inlineStr">
         <is>
           <t>-</t>
@@ -40034,19 +40058,19 @@
         </is>
       </c>
       <c r="P324" s="5" t="n">
-        <v>-0.5321979999999999</v>
+        <v>0.5321979999999999</v>
       </c>
       <c r="Q324" s="5" t="n">
-        <v>-0.676222</v>
+        <v>0.676222</v>
       </c>
       <c r="R324" s="5" t="n">
-        <v>-0.551872</v>
+        <v>0.551872</v>
       </c>
       <c r="S324" s="5" t="n">
-        <v>-0.491795</v>
+        <v>0.491795</v>
       </c>
       <c r="T324" s="5" t="n">
-        <v>-1.50181</v>
+        <v>1.50181</v>
       </c>
       <c r="U324" t="inlineStr">
         <is>
@@ -40159,7 +40183,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -40173,13 +40197,13 @@
         </is>
       </c>
       <c r="G326" s="5" t="n">
-        <v>-0.1455</v>
+        <v>0.1455</v>
       </c>
       <c r="H326" s="5" t="n">
-        <v>-0.165012</v>
+        <v>0.165012</v>
       </c>
       <c r="I326" s="5" t="n">
-        <v>-0.314172</v>
+        <v>0.314172</v>
       </c>
       <c r="J326" t="inlineStr">
         <is>
@@ -40187,13 +40211,13 @@
         </is>
       </c>
       <c r="K326" s="5" t="n">
-        <v>-0.5838410000000001</v>
+        <v>0.5838410000000001</v>
       </c>
       <c r="L326" s="5" t="n">
-        <v>-0.294692</v>
+        <v>0.294692</v>
       </c>
       <c r="M326" s="5" t="n">
-        <v>-0.30422</v>
+        <v>0.30422</v>
       </c>
       <c r="N326" t="inlineStr">
         <is>
@@ -40206,19 +40230,19 @@
         </is>
       </c>
       <c r="P326" s="5" t="n">
-        <v>-0.094371</v>
+        <v>0.094371</v>
       </c>
       <c r="Q326" s="5" t="n">
-        <v>-0.060519</v>
+        <v>0.060519</v>
       </c>
       <c r="R326" s="5" t="n">
-        <v>-0.054691</v>
+        <v>0.054691</v>
       </c>
       <c r="S326" s="5" t="n">
-        <v>-0.050322</v>
+        <v>0.050322</v>
       </c>
       <c r="T326" s="5" t="n">
-        <v>-0.050143</v>
+        <v>0.050143</v>
       </c>
       <c r="U326" t="inlineStr">
         <is>
@@ -44227,23 +44251,27 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D368" t="inlineStr"/>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E368" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F368" s="5" t="n">
-        <v>-1.424839</v>
+        <v>1.424839</v>
       </c>
       <c r="G368" s="5" t="n">
-        <v>-1.113752</v>
+        <v>1.113752</v>
       </c>
       <c r="H368" s="5" t="n">
-        <v>-1.299399</v>
+        <v>1.299399</v>
       </c>
       <c r="I368" s="5" t="n">
-        <v>-2.357085</v>
+        <v>2.357085</v>
       </c>
       <c r="J368" t="inlineStr">
         <is>
@@ -44251,13 +44279,13 @@
         </is>
       </c>
       <c r="K368" s="5" t="n">
-        <v>-6.896651</v>
+        <v>6.896651</v>
       </c>
       <c r="L368" s="5" t="n">
-        <v>-6.620604</v>
+        <v>6.620604</v>
       </c>
       <c r="M368" s="5" t="n">
-        <v>-5.666737</v>
+        <v>5.666737</v>
       </c>
       <c r="N368" t="inlineStr">
         <is>
@@ -46848,7 +46876,7 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
@@ -46857,10 +46885,10 @@
         </is>
       </c>
       <c r="F395" s="5" t="n">
-        <v>-0.1455</v>
+        <v>0.1455</v>
       </c>
       <c r="G395" s="5" t="n">
-        <v>-0.1455</v>
+        <v>0.1455</v>
       </c>
       <c r="H395" t="inlineStr">
         <is>
